--- a/arquivos/Nossa Saúde - Campos Gerais.xlsx
+++ b/arquivos/Nossa Saúde - Campos Gerais.xlsx
@@ -1057,7 +1057,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Contato: Alan Vinicius Dall Alba · (41) 99547-6715 · alan.vinicius@mazzabroker.com.br</t>
+          <t>Contato: Alan Vinicius Dall Alba · Corretor de saúde · (41) 99547-6715 · alan.vinicius@mazzabroker.com.br</t>
         </is>
       </c>
     </row>
